--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
@@ -141,10 +141,6 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">08h55
-10/03/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">09h50
 10/03/2026</t>
   </si>
@@ -209,11 +205,11 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">15h11
+    <t xml:space="preserve">15h00
 10/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">17h40
+    <t xml:space="preserve">17h20
 10/03/2026</t>
   </si>
   <si>
@@ -1288,10 +1284,10 @@
         <v>40</v>
       </c>
       <c r="D14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>41</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>42</v>
       </c>
       <c r="F14" s="15">
         <v>-21</v>
@@ -1300,33 +1296,33 @@
         <v>-25.1</v>
       </c>
       <c r="H14" s="15">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="15">
         <v>4.1</v>
       </c>
       <c r="J14" s="18">
-        <v>4.47</v>
+        <v>3.78</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>46</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>47</v>
       </c>
       <c r="F15" s="19">
         <v>-25.1</v>
@@ -1344,24 +1340,24 @@
         <v>2.99</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>51</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>52</v>
       </c>
       <c r="F16" s="22">
         <v>-35.4</v>
@@ -1379,24 +1375,24 @@
         <v>6</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>56</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>57</v>
       </c>
       <c r="F17" s="25">
         <v>-38.1</v>
@@ -1414,24 +1410,24 @@
         <v>2.46</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="30" t="s">
         <v>61</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>62</v>
       </c>
       <c r="F18" s="28">
         <v>-39.7</v>
@@ -1440,21 +1436,21 @@
         <v>-45</v>
       </c>
       <c r="H18" s="28">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="I18" s="28">
         <v>5.3</v>
       </c>
       <c r="J18" s="18">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1560,31 +1556,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1694,13 +1690,13 @@
         <v>-25.1</v>
       </c>
       <c r="G5" s="15">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="H5" s="15">
         <v>4.1</v>
       </c>
       <c r="I5" s="18">
-        <v>4.47</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1711,7 +1707,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1740,7 +1736,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1769,7 +1765,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1798,7 +1794,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1810,24 +1806,24 @@
         <v>-45</v>
       </c>
       <c r="G9" s="28">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="H9" s="28">
         <v>5.3</v>
       </c>
       <c r="I9" s="18">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>74</v>
-      </c>
       <c r="C10" s="33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
@@ -1839,7 +1835,7 @@
         <v>-45</v>
       </c>
       <c r="G10" s="33">
-        <v>9.2</v>
+        <v>9.22</v>
       </c>
       <c r="H10" s="33">
         <v>41.89</v>

--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-9</t>
+    <t>P7-09</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
   <si>
     <t>Dự án</t>
   </si>
@@ -38,10 +38,10 @@
     <t>P7-09</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KL-002</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>KL-0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -92,10 +92,10 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07h30
@@ -122,10 +122,7 @@
     <t>Gồm 2 phân đoạn: 6.68m và 2.86m</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Sét - đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08h45
@@ -165,10 +162,10 @@
     <t>Chiều dài lớp: 10.3m</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">13h35
@@ -182,10 +179,10 @@
     <t>Chiều dài lớp: 2.7m</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">14h15
@@ -199,10 +196,10 @@
     <t>Chiều dài lớp: 1.6m</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15h00
@@ -1240,19 +1237,19 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-12.69</v>
@@ -1270,24 +1267,24 @@
         <v>10.84</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>40</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="F14" s="15">
         <v>-21</v>
@@ -1305,24 +1302,24 @@
         <v>3.78</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="F15" s="19">
         <v>-25.1</v>
@@ -1340,24 +1337,24 @@
         <v>2.99</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>50</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>51</v>
       </c>
       <c r="F16" s="22">
         <v>-35.4</v>
@@ -1375,24 +1372,24 @@
         <v>6</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>55</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>56</v>
       </c>
       <c r="F17" s="25">
         <v>-38.1</v>
@@ -1410,24 +1407,24 @@
         <v>2.46</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="30" t="s">
         <v>60</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>61</v>
       </c>
       <c r="F18" s="28">
         <v>-39.7</v>
@@ -1445,12 +1442,12 @@
         <v>2.27</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1556,31 +1553,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1649,7 +1646,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1678,7 +1675,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1707,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1736,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1765,7 +1762,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1794,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1817,13 +1814,13 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>73</v>
-      </c>
       <c r="C10" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KL-0001</t>
+    <t>KCL-0001</t>
   </si>
   <si>
     <t>Đường kính</t>

--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KCL-0001</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07h30
@@ -109,10 +109,10 @@
     <t>Chiều dài lớp: 3.11m</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">07h59
@@ -122,6 +122,9 @@
     <t>Gồm 2 phân đoạn: 6.68m và 2.86m</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
@@ -145,10 +148,7 @@
     <t>Chiều dài lớp: 4.1m</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>5</t>
   </si>
   <si>
     <t xml:space="preserve">09h52
@@ -182,7 +182,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14h15
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -1237,19 +1234,19 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="12">
         <v>-12.69</v>
@@ -1267,24 +1264,24 @@
         <v>10.84</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" s="15">
         <v>-21</v>
@@ -1302,18 +1299,18 @@
         <v>3.78</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>44</v>
@@ -1646,7 +1643,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1675,7 +1672,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1704,7 +1701,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1817,10 +1814,10 @@
         <v>71</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -1814,10 +1817,10 @@
         <v>71</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/c566e3e8-1398-44c2-896a-f1c7096ebf6b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-9_D800_10-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>SGCT-KCN0003</t>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
